--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487994_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487994_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.851</v>
+        <v>12.7026</v>
       </c>
       <c r="E2" t="n">
-        <v>8.654999999999999</v>
+        <v>8.0992</v>
       </c>
       <c r="F2" t="n">
-        <v>6.196</v>
+        <v>4.6034</v>
       </c>
       <c r="G2" t="n">
-        <v>5.056</v>
+        <v>6.5294</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2462</v>
+        <v>5.6359</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8098</v>
+        <v>0.8935</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2267</v>
+        <v>7.2321</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>5.8181</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5268</v>
+        <v>1.414</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1708</v>
+        <v>-0.7027</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4538</v>
+        <v>-0.1822</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2831</v>
+        <v>-0.5205</v>
       </c>
       <c r="P2" t="n">
-        <v>3.7662</v>
+        <v>2.9733</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R2" t="n">
-        <v>4.7574</v>
+        <v>4.9556</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8217</v>
+        <v>2.0631</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2123</v>
+        <v>1.7126</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6094</v>
+        <v>0.3504</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2071</v>
+        <v>1.1367</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2071</v>
+        <v>1.1367</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>11.5154</v>
+        <v>12.621</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0805</v>
+        <v>7.1269</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4349</v>
+        <v>5.494</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5294</v>
+        <v>5.056</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6359</v>
+        <v>3.2462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8935</v>
+        <v>1.8098</v>
       </c>
       <c r="J3" t="n">
-        <v>7.2321</v>
+        <v>5.2267</v>
       </c>
       <c r="K3" t="n">
-        <v>5.8181</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.414</v>
+        <v>1.5268</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7027</v>
+        <v>-0.1708</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1822</v>
+        <v>-0.4538</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5205</v>
+        <v>0.2831</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9733</v>
+        <v>3.7662</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>4.9556</v>
+        <v>4.7574</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8759</v>
+        <v>2.5916</v>
       </c>
       <c r="T3" t="n">
-        <v>0.694</v>
+        <v>1.6842</v>
       </c>
       <c r="U3" t="n">
-        <v>0.182</v>
+        <v>0.9074</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1367</v>
+        <v>1.2071</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1367</v>
+        <v>1.2071</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>10.1274</v>
+        <v>11.058</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8785</v>
+        <v>5.3879</v>
       </c>
       <c r="F4" t="n">
-        <v>5.2489</v>
+        <v>5.6701</v>
       </c>
       <c r="G4" t="n">
         <v>4.3649</v>
@@ -766,13 +766,13 @@
         <v>4.3609</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7030999999999999</v>
+        <v>1.6336</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3196</v>
+        <v>0.8289</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3835</v>
+        <v>0.8047</v>
       </c>
       <c r="V4" t="n">
         <v>2.6808</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>7.5538</v>
+        <v>6.7388</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9681</v>
+        <v>2.1532</v>
       </c>
       <c r="F5" t="n">
         <v>4.5857</v>
@@ -844,10 +844,10 @@
         <v>3.1716</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0777</v>
+        <v>1.2628</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1014</v>
+        <v>0.2865</v>
       </c>
       <c r="U5" t="n">
         <v>0.9762999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>6.3567</v>
+        <v>6.7361</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1114</v>
+        <v>1.5188</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2453</v>
+        <v>5.2173</v>
       </c>
       <c r="G6" t="n">
         <v>3.9514</v>
@@ -922,13 +922,13 @@
         <v>2.5769</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7521</v>
+        <v>1.1315</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0696</v>
+        <v>0.3378</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8217</v>
+        <v>0.7937</v>
       </c>
       <c r="V6" t="n">
         <v>0.0674</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6304</v>
+        <v>5.1689</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5587</v>
+        <v>1.9849</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0717</v>
+        <v>3.184</v>
       </c>
       <c r="G7" t="n">
         <v>1.173</v>
@@ -1000,13 +1000,13 @@
         <v>3.7662</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1968</v>
+        <v>1.3417</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6129</v>
+        <v>0.8132</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4162</v>
+        <v>0.5285</v>
       </c>
       <c r="V7" t="n">
         <v>0.8701</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>R. CALDERON QUINONES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.4658</v>
+        <v>3.2233</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5525</v>
+        <v>3.083</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9134</v>
+        <v>0.1403</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4634</v>
+        <v>2.5095</v>
       </c>
       <c r="H8" t="n">
-        <v>1.067</v>
+        <v>0.4355</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5304</v>
+        <v>2.0739</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0791</v>
+        <v>2.1544</v>
       </c>
       <c r="K8" t="n">
-        <v>1.191</v>
+        <v>0.222</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2701</v>
+        <v>1.9324</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3843</v>
+        <v>0.3551</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1241</v>
+        <v>0.2136</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2602</v>
+        <v>0.1415</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5858</v>
+        <v>0.9911</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5769</v>
+        <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>2.61</v>
+        <v>1.1994</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6227</v>
+        <v>0.4461</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9873</v>
+        <v>0.7533</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2666</v>
+        <v>-1.4767</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2666</v>
+        <v>-2.9504</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. CALDERON QUINONES</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.2723</v>
+        <v>2.7776</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8793</v>
+        <v>0.145</v>
       </c>
       <c r="F9" t="n">
-        <v>0.393</v>
+        <v>2.6326</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5095</v>
+        <v>-0.4634</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4355</v>
+        <v>1.067</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0739</v>
+        <v>-1.5304</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1544</v>
+        <v>-0.0791</v>
       </c>
       <c r="K9" t="n">
-        <v>0.222</v>
+        <v>1.191</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9324</v>
+        <v>-1.2701</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3551</v>
+        <v>-0.3843</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2136</v>
+        <v>-0.1241</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1415</v>
+        <v>-0.2602</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9911</v>
+        <v>1.5858</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9822</v>
+        <v>2.5769</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2484</v>
+        <v>1.9217</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2423</v>
+        <v>1.2152</v>
       </c>
       <c r="U9" t="n">
-        <v>1.006</v>
+        <v>0.7065</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4767</v>
+        <v>-0.2666</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.9504</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0128</v>
+        <v>0.9141</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0845</v>
+        <v>0.677</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0717</v>
+        <v>0.2372</v>
       </c>
       <c r="G10" t="n">
         <v>0.9605</v>
@@ -1234,13 +1234,13 @@
         <v>1.784</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0026</v>
+        <v>0.904</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9325</v>
+        <v>0.525</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0701</v>
+        <v>0.379</v>
       </c>
       <c r="V10" t="n">
         <v>-1.7433</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2339</v>
+        <v>-0.3887</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8247</v>
+        <v>-1.2322</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5908</v>
+        <v>0.8435</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7641</v>
@@ -1390,13 +1390,13 @@
         <v>2.7751</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5598</v>
+        <v>1.4051</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4244</v>
+        <v>1.017</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1354</v>
+        <v>0.3881</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8137</v>
@@ -1426,10 +1426,10 @@
         <v>62.1544</v>
       </c>
       <c r="E13" t="n">
-        <v>29.54649999999999</v>
+        <v>29.5464</v>
       </c>
       <c r="F13" t="n">
-        <v>32.608</v>
+        <v>32.6081</v>
       </c>
       <c r="G13" t="n">
         <v>26.7517</v>
@@ -1471,10 +1471,10 @@
         <v>15.4545</v>
       </c>
       <c r="T13" t="n">
-        <v>8.8667</v>
+        <v>8.8665</v>
       </c>
       <c r="U13" t="n">
-        <v>6.5879</v>
+        <v>6.587899999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0.1256000000000006</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0171</v>
+        <v>0.6377</v>
       </c>
       <c r="E14" t="n">
-        <v>1.543</v>
+        <v>1.1356</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.526</v>
+        <v>-0.4979</v>
       </c>
       <c r="G14" t="n">
         <v>0.3192</v>
@@ -1546,13 +1546,13 @@
         <v>0.3964</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3014</v>
+        <v>-0.078</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5543</v>
+        <v>0.1469</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2529</v>
+        <v>-0.2249</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.2278</v>
+        <v>-2.9868</v>
       </c>
       <c r="E15" t="n">
-        <v>0.802</v>
+        <v>0.5982</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.0298</v>
+        <v>-3.5851</v>
       </c>
       <c r="G15" t="n">
         <v>-3.1496</v>
@@ -1624,13 +1624,13 @@
         <v>1.3876</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9415</v>
+        <v>-1.7005</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3816</v>
+        <v>-0.5854</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.5598</v>
+        <v>-1.1151</v>
       </c>
       <c r="V15" t="n">
         <v>0.674</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.3944</v>
+        <v>-4.3428</v>
       </c>
       <c r="E16" t="n">
         <v>-1.5884</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.806</v>
+        <v>-2.7544</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9778</v>
@@ -1702,13 +1702,13 @@
         <v>0.9911</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6237</v>
+        <v>-1.5721</v>
       </c>
       <c r="T16" t="n">
         <v>-0.7377</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8859</v>
+        <v>-0.8343</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6036</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.727</v>
+        <v>-4.5305</v>
       </c>
       <c r="E17" t="n">
         <v>-3.1092</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6179</v>
+        <v>-1.4213</v>
       </c>
       <c r="G17" t="n">
         <v>-2.1696</v>
@@ -1780,13 +1780,13 @@
         <v>0.7929</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="T17" t="n">
         <v>-0.4881</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2764</v>
+        <v>-0.0799</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6036</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.4674</v>
+        <v>-5.4779</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.4583</v>
+        <v>-3.3565</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0091</v>
+        <v>-2.1214</v>
       </c>
       <c r="G18" t="n">
         <v>-3.1811</v>
@@ -1858,13 +1858,13 @@
         <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4934</v>
+        <v>-0.5038</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3634</v>
+        <v>-0.2615</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.13</v>
+        <v>-0.2423</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6036</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.7144</v>
+        <v>-5.6583</v>
       </c>
       <c r="E19" t="n">
         <v>-2.9114</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8031</v>
+        <v>-2.7469</v>
       </c>
       <c r="G19" t="n">
         <v>-4.6091</v>
@@ -1936,13 +1936,13 @@
         <v>0.5947</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1409</v>
+        <v>-1.0847</v>
       </c>
       <c r="T19" t="n">
         <v>-0.8112</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3297</v>
+        <v>-0.2735</v>
       </c>
       <c r="V19" t="n">
         <v>2.4142</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. SENZI KITAMBO</t>
+          <t>J. PEREZ CABELLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.1747</v>
+        <v>-6.9612</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.632</v>
+        <v>-1.782</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.5427</v>
+        <v>-5.1791</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0601</v>
+        <v>-2.0575</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6422</v>
+        <v>-1.2501</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4179</v>
+        <v>-0.8074</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2977</v>
+        <v>0.3781</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3892</v>
+        <v>0.4105</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6869</v>
+        <v>-0.0324</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.3579</v>
+        <v>-2.4356</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2531</v>
+        <v>-1.6605</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.1048</v>
+        <v>-0.775</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.3698</v>
+        <v>-1.1893</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9822</v>
+        <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8569</v>
+        <v>-1.9474</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1635</v>
+        <v>-0.9708</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6934</v>
+        <v>-0.9766</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8701</v>
+        <v>-3.5509</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4737</v>
+        <v>-3.5509</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PEREZ CABELLO</t>
+          <t>E. SENZI KITAMBO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.3243</v>
+        <v>-7.1029</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9858</v>
+        <v>-3.3264</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.3385</v>
+        <v>-3.7765</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0575</v>
+        <v>-3.0601</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2501</v>
+        <v>-1.6422</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8074</v>
+        <v>-1.4179</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3781</v>
+        <v>0.2977</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4105</v>
+        <v>-0.3892</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0324</v>
+        <v>0.6869</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4356</v>
+        <v>-3.3579</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6605</v>
+        <v>-1.2531</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.775</v>
+        <v>-2.1048</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5947</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1893</v>
+        <v>-3.3698</v>
       </c>
       <c r="R21" t="n">
-        <v>1.784</v>
+        <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.3105</v>
+        <v>-1.785</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1745</v>
+        <v>-0.8579</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.136</v>
+        <v>-0.9272</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.5509</v>
+        <v>-0.8701</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.5509</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-11.2512</v>
+        <v>-10.3932</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.9477</v>
+        <v>-7.6421</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3036</v>
+        <v>-2.7511</v>
       </c>
       <c r="G22" t="n">
         <v>0.5268</v>
@@ -2170,13 +2170,13 @@
         <v>2.1805</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.5497</v>
+        <v>-2.6917</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4131</v>
+        <v>-1.1075</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.1367</v>
+        <v>-1.5842</v>
       </c>
       <c r="V22" t="n">
         <v>1.8811</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-13.89</v>
+        <v>-13.9801</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.3201</v>
+        <v>-10.6257</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5699</v>
+        <v>-3.3544</v>
       </c>
       <c r="G23" t="n">
         <v>-8.3927</v>
@@ -2248,13 +2248,13 @@
         <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0748</v>
+        <v>-2.1649</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6091</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.4657</v>
+        <v>-1.2502</v>
       </c>
       <c r="V23" t="n">
         <v>1.1367</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-62.1541</v>
+        <v>-60.796</v>
       </c>
       <c r="E24" t="n">
         <v>-32.6079</v>
       </c>
       <c r="F24" t="n">
-        <v>-29.5466</v>
+        <v>-28.1881</v>
       </c>
       <c r="G24" t="n">
         <v>-26.75149999999999</v>
@@ -2326,13 +2326,13 @@
         <v>12.8845</v>
       </c>
       <c r="S24" t="n">
-        <v>-15.4546</v>
+        <v>-14.0961</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.587899999999999</v>
+        <v>-6.587999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.8665</v>
+        <v>-7.5082</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1258000000000001</v>
